--- a/data/trans_orig/P04B1_2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258020</t>
+          <t>257454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284864</t>
+          <t>286423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242765</t>
+          <t>241690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>261562</t>
+          <t>260795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508575</t>
+          <t>507860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>542247</t>
+          <t>544588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53423</t>
+          <t>53989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92502</t>
+          <t>93217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>421775</t>
+          <t>423358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>462432</t>
+          <t>464137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>404205</t>
+          <t>403100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>437502</t>
+          <t>437144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>835968</t>
+          <t>837080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>889830</t>
+          <t>890030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55958</t>
+          <t>54253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96615</t>
+          <t>95032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77467</t>
+          <t>77825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110764</t>
+          <t>111869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143529</t>
+          <t>143329</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197391</t>
+          <t>196279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>228565</t>
+          <t>227872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256973</t>
+          <t>256766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>258916</t>
+          <t>258745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284634</t>
+          <t>285145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>495337</t>
+          <t>496922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>533339</t>
+          <t>532680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58061</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86469</t>
+          <t>87162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64494</t>
+          <t>63983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90212</t>
+          <t>90383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130822</t>
+          <t>131481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168824</t>
+          <t>167239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>203330</t>
+          <t>201143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>240020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354564</t>
+          <t>352361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>420094</t>
+          <t>419080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>564835</t>
+          <t>569471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>653479</t>
+          <t>654175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70531</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109227</t>
+          <t>111414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120992</t>
+          <t>123195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134634</t>
+          <t>133938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223278</t>
+          <t>218642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111842</t>
+          <t>111893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133441</t>
+          <t>133259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197892</t>
+          <t>197722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233715</t>
+          <t>234354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>318519</t>
+          <t>317014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369510</t>
+          <t>367837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45301</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66900</t>
+          <t>66849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25064</t>
+          <t>24425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60887</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>69684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119002</t>
+          <t>120507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214964</t>
+          <t>213638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236218</t>
+          <t>235820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218666</t>
+          <t>217979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234857</t>
+          <t>234738</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>439286</t>
+          <t>438980</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>464831</t>
+          <t>466411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>55131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>59414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86539</t>
+          <t>86845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>412801</t>
+          <t>411640</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>464861</t>
+          <t>463541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>532293</t>
+          <t>534946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>730927</t>
+          <t>730903</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>975813</t>
+          <t>972987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1220813</t>
+          <t>1202589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156107</t>
+          <t>157427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208167</t>
+          <t>209328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116332</t>
+          <t>116356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314966</t>
+          <t>312313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247414</t>
+          <t>265638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>492414</t>
+          <t>495240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128455</t>
+          <t>129360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>662990</t>
+          <t>662040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79590</t>
+          <t>78447</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115927</t>
+          <t>113190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>221195</t>
+          <t>219974</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>901863</t>
+          <t>886568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>265730</t>
+          <t>266680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>800265</t>
+          <t>799360</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>601163</t>
+          <t>603900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>637500</t>
+          <t>638643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>743947</t>
+          <t>759242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1424615</t>
+          <t>1425836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2213853</t>
+          <t>2218726</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2551761</t>
+          <t>2597903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2369045</t>
+          <t>2370128</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2680116</t>
+          <t>2693560</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4623740</t>
+          <t>4631446</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5098632</t>
+          <t>5102104</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>902861</t>
+          <t>856719</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1240769</t>
+          <t>1235896</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1029355</t>
+          <t>1015911</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1340426</t>
+          <t>1339343</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2065461</t>
+          <t>2061989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2540353</t>
+          <t>2532647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>274463</t>
+          <t>278319</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257454</t>
+          <t>265793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286423</t>
+          <t>289569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>252943</t>
+          <t>271474</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>241690</t>
+          <t>259126</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260795</t>
+          <t>280270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>527405</t>
+          <t>549793</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507860</t>
+          <t>533826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>544588</t>
+          <t>565300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25020</t>
+          <t>29276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53989</t>
+          <t>53052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36692</t>
+          <t>44587</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>56935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>73672</t>
+          <t>85113</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93217</t>
+          <t>101080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>444785</t>
+          <t>455815</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>423358</t>
+          <t>434794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>464137</t>
+          <t>474078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>420551</t>
+          <t>446710</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>403100</t>
+          <t>428564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>437144</t>
+          <t>462043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>865336</t>
+          <t>902525</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>837080</t>
+          <t>877205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>890030</t>
+          <t>926609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>73605</t>
+          <t>74832</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95032</t>
+          <t>95853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94418</t>
+          <t>99784</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77825</t>
+          <t>84451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111869</t>
+          <t>117930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>168023</t>
+          <t>174616</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143329</t>
+          <t>150532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196279</t>
+          <t>199936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>243516</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>227872</t>
+          <t>227583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256766</t>
+          <t>254009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>272290</t>
+          <t>277209</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>258745</t>
+          <t>263921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285145</t>
+          <t>289870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>515805</t>
+          <t>518316</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496922</t>
+          <t>499060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>532680</t>
+          <t>536508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>73908</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>61005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87162</t>
+          <t>87431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76838</t>
+          <t>79172</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63983</t>
+          <t>66511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90383</t>
+          <t>92460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>148356</t>
+          <t>153080</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131481</t>
+          <t>134888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167239</t>
+          <t>172336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>315014</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>315014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>315014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>222814</t>
+          <t>275566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201143</t>
+          <t>250660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240020</t>
+          <t>294296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381220</t>
+          <t>313224</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352361</t>
+          <t>295532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>419080</t>
+          <t>327768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>604034</t>
+          <t>588790</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>569471</t>
+          <t>559491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>654175</t>
+          <t>614429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>97579</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>78849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111414</t>
+          <t>122485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94336</t>
+          <t>107769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56476</t>
+          <t>93225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123195</t>
+          <t>125461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>184079</t>
+          <t>205348</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133938</t>
+          <t>179709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218642</t>
+          <t>234647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>123191</t>
+          <t>138026</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>124178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133259</t>
+          <t>148995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>213451</t>
+          <t>177832</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197722</t>
+          <t>166559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>234354</t>
+          <t>185934</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>336642</t>
+          <t>315857</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>317014</t>
+          <t>299385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367837</t>
+          <t>331284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>67639</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66849</t>
+          <t>81487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>51086</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>62359</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>118725</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69684</t>
+          <t>103298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120507</t>
+          <t>135197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>226093</t>
+          <t>221017</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213638</t>
+          <t>207668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>235820</t>
+          <t>231306</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>227428</t>
+          <t>232630</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>217979</t>
+          <t>223055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234738</t>
+          <t>240307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>453521</t>
+          <t>453648</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>438980</t>
+          <t>437775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>466411</t>
+          <t>465829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42676</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>62201</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29628</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>40695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72304</t>
+          <t>79972</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>95845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268769</t>
+          <t>269869</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>438869</t>
+          <t>497336</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>411640</t>
+          <t>466013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463541</t>
+          <t>523736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>616073</t>
+          <t>494093</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>534946</t>
+          <t>470108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>730903</t>
+          <t>519861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1054942</t>
+          <t>991429</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>972987</t>
+          <t>954578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1202589</t>
+          <t>1030020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>182099</t>
+          <t>216277</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157427</t>
+          <t>189877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209328</t>
+          <t>247600</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>231186</t>
+          <t>275803</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116356</t>
+          <t>250035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>312313</t>
+          <t>299788</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413285</t>
+          <t>492080</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265638</t>
+          <t>453489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>495240</t>
+          <t>528931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620968</t>
+          <t>713613</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620968</t>
+          <t>713613</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620968</t>
+          <t>713613</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847259</t>
+          <t>769896</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847259</t>
+          <t>769896</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847259</t>
+          <t>769896</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1468227</t>
+          <t>1483509</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1468227</t>
+          <t>1483509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1468227</t>
+          <t>1483509</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>344754</t>
+          <t>113951</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129360</t>
+          <t>94584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>662040</t>
+          <t>137986</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>94411</t>
+          <t>104731</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78447</t>
+          <t>88652</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>120937</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>439166</t>
+          <t>218682</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>219974</t>
+          <t>193065</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>886568</t>
+          <t>250401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>583966</t>
+          <t>684121</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>266680</t>
+          <t>660086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>799360</t>
+          <t>703488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>622679</t>
+          <t>725923</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>603900</t>
+          <t>709717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>638643</t>
+          <t>742002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1206644</t>
+          <t>1410044</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>759242</t>
+          <t>1378325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1425836</t>
+          <t>1435661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717090</t>
+          <t>830654</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717090</t>
+          <t>830654</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717090</t>
+          <t>830654</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645810</t>
+          <t>1628726</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645810</t>
+          <t>1628726</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645810</t>
+          <t>1628726</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2318485</t>
+          <t>2221137</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2218726</t>
+          <t>2159459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2597903</t>
+          <t>2279291</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2478366</t>
+          <t>2317903</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2370128</t>
+          <t>2264233</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2693560</t>
+          <t>2373117</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4796851</t>
+          <t>4539040</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4631446</t>
+          <t>4459440</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5102104</t>
+          <t>4619412</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1136137</t>
+          <t>1303734</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>856719</t>
+          <t>1245580</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1235896</t>
+          <t>1365412</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1231105</t>
+          <t>1415244</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015911</t>
+          <t>1360030</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1339343</t>
+          <t>1468914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2367242</t>
+          <t>2718978</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2061989</t>
+          <t>2638606</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2532647</t>
+          <t>2798578</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
